--- a/Assets/Excal/TowerInfo.xlsx
+++ b/Assets/Excal/TowerInfo.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="11190"/>
+    <workbookView windowWidth="22185" windowHeight="9720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1080,14 +1080,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="5" max="5" width="9.54545454545454" customWidth="1"/>
-    <col min="6" max="6" width="11.8181818181818" customWidth="1"/>
-    <col min="7" max="7" width="8.54545454545454" customWidth="1"/>
+    <col min="5" max="5" width="9.54166666666667" customWidth="1"/>
+    <col min="6" max="6" width="11.8166666666667" customWidth="1"/>
+    <col min="7" max="7" width="8.54166666666667" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="10.6363636363636" customWidth="1"/>
-    <col min="11" max="11" width="10.6363636363636" customWidth="1"/>
+    <col min="9" max="9" width="10.6333333333333" customWidth="1"/>
+    <col min="11" max="11" width="10.6333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1451,7 +1451,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1463,7 +1463,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
